--- a/input/timetable/Менеджмент.xlsx
+++ b/input/timetable/Менеджмент.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>

--- a/input/timetable/Менеджмент.xlsx
+++ b/input/timetable/Менеджмент.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="148">
   <si>
     <t>пара</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -128,12 +131,36 @@
     <t>ЭУК</t>
   </si>
   <si>
+    <t>Стрих Н.И.</t>
+  </si>
+  <si>
+    <t>Попова Е.В.</t>
+  </si>
+  <si>
+    <t>Курамшина А.В.</t>
+  </si>
+  <si>
+    <t>Собиров Б.Ш.</t>
+  </si>
+  <si>
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Заведеев Е.В.</t>
+  </si>
+  <si>
+    <t>Исаева И.А.</t>
+  </si>
+  <si>
+    <t>Колосова О.Г.</t>
+  </si>
+  <si>
+    <t>Антонов С.А.</t>
+  </si>
+  <si>
     <t>Организация оплаты труда (лек), К512</t>
   </si>
   <si>
@@ -143,18 +170,33 @@
     <t>Планирование и организация производства на предприятиях нефтяной и газовой промышленности</t>
   </si>
   <si>
+    <t>Лешукова Е.В.</t>
+  </si>
+  <si>
+    <t>Вариясова Е.В.</t>
+  </si>
+  <si>
     <t>Психология инклюзивного общества (лекция 16 ч)</t>
   </si>
   <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
     <t>403-41</t>
   </si>
   <si>
+    <t>Муртазин Ш.Н.</t>
+  </si>
+  <si>
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
     <t>История России (лекция 32 ч)</t>
   </si>
   <si>
+    <t>Мойсеенкова М.А.</t>
+  </si>
+  <si>
     <t>ФТД: Цифровая грамотность (пр), К433</t>
   </si>
   <si>
@@ -167,6 +209,9 @@
     <t>Иностранный язык, п/г 1, К412</t>
   </si>
   <si>
+    <t>Воронина Е.В.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 2, К517</t>
   </si>
   <si>
@@ -233,6 +278,9 @@
     <t>Экономическая оценка инвестиций (пр)  К511//</t>
   </si>
   <si>
+    <t>Антонов Л.А.</t>
+  </si>
+  <si>
     <t>ФТД: Финансовые расчеты в управлении (лек), К429//</t>
   </si>
   <si>
@@ -242,18 +290,30 @@
     <t>Управление затратами (лек), К511//</t>
   </si>
   <si>
+    <t>Малагин Д.В.</t>
+  </si>
+  <si>
     <t>Управление затратами (пр), К518</t>
   </si>
   <si>
     <t>Анализ и диагностика финансово-хозяйственной деятельности корпораций (лек), К511//</t>
   </si>
   <si>
+    <t>Усаева Н.Р./Заведеев Е.В.</t>
+  </si>
+  <si>
     <t>Управление конкурентоспособностью организации (лек)/(пр), К511</t>
   </si>
   <si>
+    <t>Клишин А.С.</t>
+  </si>
+  <si>
     <t>Транспорт, хранение и сбыт нефти, нефтепродуктов и газа (лек)/(пр), К511</t>
   </si>
   <si>
+    <t>Гаврилов А.С.</t>
+  </si>
+  <si>
     <t>Организация производства на предприятиях нефтяной и газовой промышленности (лек)/(пр), К511</t>
   </si>
   <si>
@@ -272,15 +332,27 @@
     <t>Финансовые рынки и институты (лек)/(пр), К511</t>
   </si>
   <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
+    <t>Костюнина М.В.</t>
+  </si>
+  <si>
     <t>Менеджмент (лек), К201//</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>Литовченко А.С.</t>
+  </si>
+  <si>
     <t>День самостоятельной работы</t>
   </si>
   <si>
+    <t>Смирнова И.В./Собиров Б.Ш.</t>
+  </si>
+  <si>
     <t>Корпоративная социальная ответственность (лек)/(пр), К508</t>
   </si>
   <si>
@@ -302,7 +374,25 @@
     <t>//Организация коммерческой деятельности (пр), К512</t>
   </si>
   <si>
+    <t>Осипова .А.В.</t>
+  </si>
+  <si>
+    <t>Осипова А.В.</t>
+  </si>
+  <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
+    <t>Наумова А.А.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
+  </si>
+  <si>
+    <t>Бутенко Н.А.</t>
+  </si>
+  <si>
+    <t>Стрих Н.И./Курамшина А.В.</t>
   </si>
   <si>
     <t xml:space="preserve"> Философия (пр), К429//</t>
@@ -495,7 +585,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -514,6 +604,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -525,7 +621,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -655,6 +751,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1186,6 +1295,32 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1227,6 +1362,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -1248,6 +1396,19 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1260,7 +1421,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="262">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1303,16 +1464,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1321,10 +1479,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1348,6 +1512,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1357,62 +1522,69 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1420,7 +1592,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1430,30 +1602,54 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1461,362 +1657,355 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2148,7 +2337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2157,10 +2346,11 @@
     <col min="4" max="4" width="18" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2168,15 +2358,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2184,39 +2374,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2226,35 +2416,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="103" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="123" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="123"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
@@ -2265,353 +2455,417 @@
       <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="23"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="G9" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="26">
         <v>2</v>
       </c>
-      <c r="C10" s="104" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="106"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="C10" s="124" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="85"/>
+    </row>
+    <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28">
         <v>3</v>
       </c>
-      <c r="C11" s="107" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="109"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="C11" s="127" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>4</v>
       </c>
-      <c r="C12" s="116" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="118"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29">
+      <c r="C12" s="136" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="137"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="138"/>
+      <c r="G12" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>5</v>
       </c>
-      <c r="C13" s="113" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="114"/>
-      <c r="E13" s="114"/>
-      <c r="F13" s="115"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="31">
+      <c r="C13" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="84" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="32">
         <v>1</v>
       </c>
-      <c r="C14" s="110" t="s">
+      <c r="C14" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="65"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
+        <v>2</v>
+      </c>
+      <c r="C15" s="139"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="86"/>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
+        <v>3</v>
+      </c>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="86"/>
+    </row>
+    <row r="17" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="33"/>
+      <c r="B17" s="30">
+        <v>4</v>
+      </c>
+      <c r="C17" s="142"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="80"/>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="32">
+        <v>1</v>
+      </c>
+      <c r="C18" s="120"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="65"/>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
+        <v>2</v>
+      </c>
+      <c r="C19" s="158"/>
+      <c r="D19" s="159"/>
+      <c r="E19" s="159"/>
+      <c r="F19" s="160"/>
+      <c r="G19" s="86"/>
+    </row>
+    <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28">
+        <v>3</v>
+      </c>
+      <c r="C20" s="139"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="153" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="154"/>
+      <c r="G20" s="86" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="33"/>
+      <c r="B21" s="30">
+        <v>5</v>
+      </c>
+      <c r="C21" s="161" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="162"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="163"/>
+      <c r="G21" s="83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="32">
+        <v>1</v>
+      </c>
+      <c r="C22" s="120"/>
+      <c r="D22" s="121"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="65"/>
+    </row>
+    <row r="23" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28">
+        <v>2</v>
+      </c>
+      <c r="C23" s="139"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="86"/>
+    </row>
+    <row r="24" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28">
+        <v>3</v>
+      </c>
+      <c r="C24" s="152" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="154"/>
+      <c r="G24" s="86" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="33"/>
+      <c r="B25" s="30">
+        <v>4</v>
+      </c>
+      <c r="C25" s="164" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="165"/>
+      <c r="E25" s="165"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="83" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="32">
+        <v>2</v>
+      </c>
+      <c r="C26" s="155"/>
+      <c r="D26" s="156"/>
+      <c r="E26" s="156"/>
+      <c r="F26" s="157"/>
+      <c r="G26" s="67"/>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="35"/>
+      <c r="B27" s="28">
+        <v>3</v>
+      </c>
+      <c r="C27" s="152" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="154"/>
+      <c r="G27" s="86" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="35"/>
+      <c r="B28" s="28">
+        <v>4</v>
+      </c>
+      <c r="C28" s="149" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="150"/>
+      <c r="E28" s="150"/>
+      <c r="F28" s="151"/>
+      <c r="G28" s="91" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="36"/>
+      <c r="B29" s="30">
+        <v>5</v>
+      </c>
+      <c r="C29" s="145" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="146"/>
+      <c r="E29" s="147"/>
+      <c r="F29" s="148"/>
+      <c r="G29" s="86" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="32">
+        <v>1</v>
+      </c>
+      <c r="C30" s="101"/>
+      <c r="D30" s="102"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="65"/>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="35"/>
+      <c r="B31" s="28">
+        <v>2</v>
+      </c>
+      <c r="C31" s="117"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="66"/>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="38"/>
+      <c r="B32" s="28">
+        <v>3</v>
+      </c>
+      <c r="C32" s="114" t="s">
+        <v>115</v>
+      </c>
+      <c r="D32" s="115"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="116"/>
+      <c r="G32" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="112"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
-        <v>2</v>
-      </c>
-      <c r="C15" s="100"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="102"/>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
-        <v>3</v>
-      </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="81"/>
-    </row>
-    <row r="17" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
-      <c r="B17" s="29">
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="30">
         <v>4</v>
       </c>
-      <c r="C17" s="119"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="121"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="31">
-        <v>1</v>
-      </c>
-      <c r="C18" s="91"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="93"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
-        <v>2</v>
-      </c>
-      <c r="C19" s="88"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="90"/>
-    </row>
-    <row r="20" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
-        <v>3</v>
-      </c>
-      <c r="C20" s="100"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="83" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="84"/>
-    </row>
-    <row r="21" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="32"/>
-      <c r="B21" s="29">
-        <v>5</v>
-      </c>
-      <c r="C21" s="94" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="96"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="31">
-        <v>1</v>
-      </c>
-      <c r="C22" s="91"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="93"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
-        <v>2</v>
-      </c>
-      <c r="C23" s="100"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="102"/>
-    </row>
-    <row r="24" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
-        <v>3</v>
-      </c>
-      <c r="C24" s="82" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="84"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="32"/>
-      <c r="B25" s="29">
-        <v>4</v>
-      </c>
-      <c r="C25" s="97" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="99"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="31">
-        <v>2</v>
-      </c>
-      <c r="C26" s="85"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="87"/>
-    </row>
-    <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="27">
-        <v>3</v>
-      </c>
-      <c r="C27" s="82" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="84"/>
-    </row>
-    <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="27">
-        <v>4</v>
-      </c>
-      <c r="C28" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78"/>
-    </row>
-    <row r="29" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="34"/>
-      <c r="B29" s="29">
-        <v>5</v>
-      </c>
-      <c r="C29" s="72" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="73"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="75"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="31">
-        <v>1</v>
-      </c>
-      <c r="C30" s="125"/>
-      <c r="D30" s="126"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="127"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="33"/>
-      <c r="B31" s="27">
-        <v>2</v>
-      </c>
-      <c r="C31" s="79"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="81"/>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="36"/>
-      <c r="B32" s="27">
-        <v>3</v>
-      </c>
-      <c r="C32" s="138" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="140"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="37"/>
-      <c r="B33" s="29">
-        <v>4</v>
-      </c>
-      <c r="C33" s="132" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="133"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="134"/>
-    </row>
-    <row r="34" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="128"/>
-      <c r="D34" s="128"/>
-      <c r="E34" s="128"/>
-      <c r="F34" s="128"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="61"/>
-      <c r="B35" s="31" t="s">
+      <c r="C33" s="108" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="110"/>
+      <c r="G33" s="83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="40"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="104"/>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="42"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="70"/>
+      <c r="B35" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="135" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="136"/>
-      <c r="E35" s="136"/>
-      <c r="F35" s="137"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="62"/>
-      <c r="B36" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="129" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="130"/>
-      <c r="E36" s="130"/>
-      <c r="F36" s="131"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="62"/>
-      <c r="B37" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="129" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="130"/>
-      <c r="E37" s="130"/>
-      <c r="F37" s="131"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="63"/>
-      <c r="B38" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="122" t="s">
-        <v>41</v>
-      </c>
-      <c r="D38" s="123"/>
-      <c r="E38" s="123"/>
-      <c r="F38" s="124"/>
-    </row>
-    <row r="39" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D35" s="112"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="85" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="71"/>
+      <c r="B36" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="105" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="106"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="107"/>
+      <c r="G36" s="86" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="71"/>
+      <c r="B37" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="105" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="91" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="72"/>
+      <c r="B38" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="98" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="100"/>
+      <c r="G38" s="83" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>15</v>
       </c>
@@ -2621,23 +2875,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C12:F12"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="C28:F28"/>
@@ -2653,6 +2890,23 @@
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C31:F31"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2683,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2692,10 +2946,11 @@
     <col min="4" max="4" width="19.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2703,15 +2958,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2719,39 +2974,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2761,47 +3016,47 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="144" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="144"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="W8" s="64"/>
-    </row>
-    <row r="9" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="192" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="192"/>
+      <c r="E8" s="192"/>
+      <c r="F8" s="192"/>
+      <c r="X8" s="73"/>
+    </row>
+    <row r="9" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="148" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="148"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="42"/>
-    </row>
-    <row r="10" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+      <c r="C9" s="196" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="196"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="45"/>
+    </row>
+    <row r="10" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>0</v>
@@ -2812,334 +3067,398 @@
       <c r="D10" s="21"/>
       <c r="E10" s="22"/>
       <c r="F10" s="23"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="25">
+      <c r="G10" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.4">
+      <c r="A11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="26">
         <v>1</v>
       </c>
-      <c r="C11" s="152" t="s">
+      <c r="C11" s="200" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="201"/>
+      <c r="E11" s="201"/>
+      <c r="F11" s="202"/>
+      <c r="G11" s="85" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
+        <v>2</v>
+      </c>
+      <c r="C12" s="136" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="137"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="138"/>
+      <c r="G12" s="86" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
+        <v>3</v>
+      </c>
+      <c r="C13" s="203" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="204"/>
+      <c r="E13" s="204"/>
+      <c r="F13" s="205"/>
+      <c r="G13" s="64"/>
+    </row>
+    <row r="14" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="32">
+        <v>2</v>
+      </c>
+      <c r="C14" s="197"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="198"/>
+      <c r="F14" s="199"/>
+      <c r="G14" s="90"/>
+    </row>
+    <row r="15" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
+        <v>3</v>
+      </c>
+      <c r="C15" s="152" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="91" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
+        <v>4</v>
+      </c>
+      <c r="C16" s="152" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="154"/>
+      <c r="G16" s="91" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28">
+        <v>5</v>
+      </c>
+      <c r="C17" s="167" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="168"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="91" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="33"/>
+      <c r="B18" s="30">
+        <v>6</v>
+      </c>
+      <c r="C18" s="206"/>
+      <c r="D18" s="207"/>
+      <c r="E18" s="207"/>
+      <c r="F18" s="208"/>
+      <c r="G18" s="64"/>
+    </row>
+    <row r="19" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="32">
+        <v>2</v>
+      </c>
+      <c r="C19" s="189" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="190"/>
+      <c r="E19" s="190"/>
+      <c r="F19" s="191"/>
+      <c r="G19" s="85" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27"/>
+      <c r="B20" s="26">
+        <v>3</v>
+      </c>
+      <c r="C20" s="212" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="213"/>
+      <c r="E20" s="213"/>
+      <c r="F20" s="214"/>
+      <c r="G20" s="91" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28">
+        <v>4</v>
+      </c>
+      <c r="C21" s="167" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="168"/>
+      <c r="E21" s="168"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="33"/>
+      <c r="B22" s="30">
+        <v>5</v>
+      </c>
+      <c r="C22" s="193"/>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="195"/>
+      <c r="G22" s="64"/>
+    </row>
+    <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="32">
+        <v>1</v>
+      </c>
+      <c r="C23" s="209" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="210"/>
+      <c r="E23" s="210"/>
+      <c r="F23" s="211"/>
+      <c r="G23" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="153"/>
-      <c r="E11" s="153"/>
-      <c r="F11" s="154"/>
-    </row>
-    <row r="12" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28">
         <v>2</v>
       </c>
-      <c r="C12" s="116" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="118"/>
-    </row>
-    <row r="13" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29">
+      <c r="C24" s="167" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="168"/>
+      <c r="E24" s="168"/>
+      <c r="F24" s="169"/>
+      <c r="G24" s="91" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28">
         <v>3</v>
       </c>
-      <c r="C13" s="155" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="157"/>
-    </row>
-    <row r="14" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="31">
-        <v>2</v>
-      </c>
-      <c r="C14" s="149"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="151"/>
-    </row>
-    <row r="15" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
-        <v>3</v>
-      </c>
-      <c r="C15" s="82" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="84"/>
-    </row>
-    <row r="16" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
-        <v>4</v>
-      </c>
-      <c r="C16" s="82" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="84"/>
-    </row>
-    <row r="17" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
-        <v>5</v>
-      </c>
-      <c r="C17" s="158" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="159"/>
-      <c r="E17" s="159"/>
-      <c r="F17" s="160"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="32"/>
-      <c r="B18" s="29">
-        <v>6</v>
-      </c>
-      <c r="C18" s="161"/>
-      <c r="D18" s="162"/>
-      <c r="E18" s="162"/>
-      <c r="F18" s="163"/>
-    </row>
-    <row r="19" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="31">
-        <v>2</v>
-      </c>
-      <c r="C19" s="141" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="143"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="25">
-        <v>3</v>
-      </c>
-      <c r="C20" s="167" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" s="168"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="169"/>
-    </row>
-    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
-        <v>4</v>
-      </c>
-      <c r="C21" s="158" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="160"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="32"/>
-      <c r="B22" s="29">
-        <v>5</v>
-      </c>
-      <c r="C22" s="145"/>
-      <c r="D22" s="146"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="147"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="31">
-        <v>1</v>
-      </c>
-      <c r="C23" s="164" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="165"/>
-      <c r="E23" s="165"/>
-      <c r="F23" s="166"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27">
-        <v>2</v>
-      </c>
-      <c r="C24" s="158" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="160"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27">
-        <v>3</v>
-      </c>
-      <c r="C25" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="78"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="32"/>
-      <c r="B26" s="29">
+      <c r="C25" s="149" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="150"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="151"/>
+      <c r="G25" s="66"/>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="33"/>
+      <c r="B26" s="30">
         <v>4</v>
       </c>
       <c r="C26" s="170"/>
       <c r="D26" s="171"/>
       <c r="E26" s="171"/>
       <c r="F26" s="172"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="G26" s="64"/>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="32">
         <v>3</v>
       </c>
       <c r="C27" s="180"/>
       <c r="D27" s="181"/>
       <c r="E27" s="181"/>
       <c r="F27" s="182"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="27">
+      <c r="G27" s="90"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="35"/>
+      <c r="B28" s="28">
         <v>4</v>
       </c>
-      <c r="C28" s="119"/>
-      <c r="D28" s="120"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="121"/>
-    </row>
-    <row r="29" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44">
+      <c r="C28" s="142"/>
+      <c r="D28" s="143"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="66"/>
+    </row>
+    <row r="29" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="46"/>
+      <c r="B29" s="47">
         <v>5</v>
       </c>
-      <c r="C29" s="158" t="s">
-        <v>46</v>
+      <c r="C29" s="167" t="s">
+        <v>60</v>
       </c>
       <c r="D29" s="183"/>
       <c r="E29" s="186"/>
-      <c r="F29" s="160"/>
-    </row>
-    <row r="30" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="34"/>
-      <c r="B30" s="29">
+      <c r="F29" s="169"/>
+      <c r="G29" s="91" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="36"/>
+      <c r="B30" s="30">
         <v>6</v>
       </c>
       <c r="C30" s="184"/>
       <c r="D30" s="185"/>
       <c r="E30" s="187" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F30" s="188"/>
-    </row>
-    <row r="31" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="31">
+      <c r="G30" s="84" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="32">
         <v>2</v>
       </c>
       <c r="C31" s="173" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="D31" s="174"/>
       <c r="E31" s="174"/>
       <c r="F31" s="175"/>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="36"/>
-      <c r="B32" s="27">
+      <c r="G31" s="85" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="38"/>
+      <c r="B32" s="28">
         <v>3</v>
       </c>
-      <c r="C32" s="158" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" s="159"/>
-      <c r="E32" s="159"/>
-      <c r="F32" s="160"/>
-    </row>
-    <row r="33" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="37"/>
-      <c r="B33" s="29">
+      <c r="C32" s="167" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="168"/>
+      <c r="E32" s="168"/>
+      <c r="F32" s="169"/>
+      <c r="G32" s="91" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="39"/>
+      <c r="B33" s="30">
         <v>4</v>
       </c>
       <c r="C33" s="177"/>
       <c r="D33" s="178"/>
       <c r="E33" s="178"/>
       <c r="F33" s="179"/>
-    </row>
-    <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="45"/>
-      <c r="B34" s="46"/>
+      <c r="G33" s="64"/>
+    </row>
+    <row r="34" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="48"/>
+      <c r="B34" s="49"/>
       <c r="C34" s="176"/>
       <c r="D34" s="176"/>
       <c r="E34" s="176"/>
       <c r="F34" s="176"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="40"/>
-      <c r="B35" s="59" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="135" t="s">
+      <c r="G34" s="50"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="43"/>
+      <c r="B35" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="136"/>
-      <c r="E35" s="136"/>
-      <c r="F35" s="137"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="47"/>
-      <c r="B36" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="129" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="130"/>
-      <c r="E36" s="130"/>
-      <c r="F36" s="131"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="49"/>
-      <c r="B37" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="122" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="124"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C35" s="111" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="112"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="113"/>
+      <c r="G35" s="87" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="51"/>
+      <c r="B36" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="105" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="106"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="107"/>
+      <c r="G36" s="93" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="53"/>
+      <c r="B37" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="98" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="92" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>15</v>
       </c>
@@ -3149,21 +3468,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C8:F8"/>
@@ -3180,6 +3484,21 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3217,7 +3536,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3226,78 +3545,79 @@
     <col min="4" max="4" width="20.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="21" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="69" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="78" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69" t="s">
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="78" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="70" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F4" s="79" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3307,349 +3627,406 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="189" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="189"/>
-      <c r="E8" s="189"/>
-      <c r="F8" s="189"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="235" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" s="235"/>
+      <c r="E8" s="235"/>
+      <c r="F8" s="235"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="54"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="D9" s="56"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="26">
         <v>2</v>
       </c>
-      <c r="C10" s="190" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="191"/>
-      <c r="E10" s="191"/>
-      <c r="F10" s="192"/>
-    </row>
-    <row r="11" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="C10" s="236" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="237"/>
+      <c r="E10" s="237"/>
+      <c r="F10" s="238"/>
+      <c r="G10" s="87" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28">
         <v>3</v>
       </c>
-      <c r="C11" s="193" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="194"/>
-      <c r="E11" s="194"/>
-      <c r="F11" s="195"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="C11" s="239" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="240"/>
+      <c r="E11" s="240"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="89" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>4</v>
       </c>
-      <c r="C12" s="193" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="194"/>
-      <c r="E12" s="194"/>
-      <c r="F12" s="195"/>
-    </row>
-    <row r="13" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29">
+      <c r="C12" s="239" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="240"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="89" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="29"/>
+      <c r="B13" s="30">
         <v>5</v>
       </c>
-      <c r="C13" s="196"/>
-      <c r="D13" s="197"/>
-      <c r="E13" s="197"/>
-      <c r="F13" s="198"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="164" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="165"/>
-      <c r="E14" s="165"/>
-      <c r="F14" s="166"/>
-    </row>
-    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="C13" s="242"/>
+      <c r="D13" s="243"/>
+      <c r="E13" s="243"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="89"/>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="209" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
+      <c r="F14" s="211"/>
+      <c r="G14" s="65"/>
+    </row>
+    <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
         <v>4</v>
       </c>
-      <c r="C15" s="82" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="84"/>
-    </row>
-    <row r="16" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+      <c r="C15" s="152" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="86" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
         <v>5</v>
       </c>
-      <c r="C16" s="116" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="118"/>
-    </row>
-    <row r="17" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="32"/>
-      <c r="B17" s="29">
+      <c r="C16" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="86" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="33"/>
+      <c r="B17" s="30">
         <v>6</v>
       </c>
-      <c r="C17" s="199"/>
-      <c r="D17" s="200"/>
-      <c r="E17" s="200"/>
-      <c r="F17" s="201"/>
-    </row>
-    <row r="18" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="31">
+      <c r="C17" s="229"/>
+      <c r="D17" s="230"/>
+      <c r="E17" s="230"/>
+      <c r="F17" s="231"/>
+      <c r="G17" s="64"/>
+    </row>
+    <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="32">
         <v>3</v>
       </c>
       <c r="C18" s="173" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D18" s="174"/>
       <c r="E18" s="174"/>
       <c r="F18" s="175"/>
-    </row>
-    <row r="19" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27">
+      <c r="G18" s="85" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28">
         <v>4</v>
       </c>
-      <c r="C19" s="158" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="159"/>
-      <c r="E19" s="159"/>
-      <c r="F19" s="160"/>
-    </row>
-    <row r="20" spans="1:6" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27">
+      <c r="C19" s="167" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="168"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="169"/>
+      <c r="G19" s="86" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28">
         <v>5</v>
       </c>
       <c r="C20" s="177"/>
       <c r="D20" s="178"/>
       <c r="E20" s="178"/>
       <c r="F20" s="179"/>
-    </row>
-    <row r="21" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="G20" s="82"/>
+    </row>
+    <row r="21" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="32">
         <v>3</v>
       </c>
-      <c r="C21" s="202" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="203"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="204"/>
-    </row>
-    <row r="22" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
+      <c r="C21" s="232" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="233"/>
+      <c r="E21" s="233"/>
+      <c r="F21" s="234"/>
+      <c r="G21" s="87" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28">
         <v>4</v>
       </c>
-      <c r="C22" s="158" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="160"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
+      <c r="C22" s="167" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="168"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="169"/>
+      <c r="G22" s="89" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28">
         <v>5</v>
       </c>
-      <c r="C23" s="158" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="159"/>
-      <c r="E23" s="159"/>
-      <c r="F23" s="160"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="32"/>
-      <c r="B24" s="29">
+      <c r="C23" s="167" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="168"/>
+      <c r="E23" s="168"/>
+      <c r="F23" s="169"/>
+      <c r="G23" s="89" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="33"/>
+      <c r="B24" s="30">
         <v>6</v>
       </c>
-      <c r="C24" s="215"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="75"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="31">
+      <c r="C24" s="225"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="148"/>
+      <c r="G24" s="81"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="32">
         <v>1</v>
       </c>
-      <c r="C25" s="206"/>
-      <c r="D25" s="207"/>
-      <c r="E25" s="207"/>
-      <c r="F25" s="208"/>
-    </row>
-    <row r="26" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="33"/>
-      <c r="B26" s="27">
+      <c r="C25" s="216"/>
+      <c r="D25" s="217"/>
+      <c r="E25" s="217"/>
+      <c r="F25" s="218"/>
+      <c r="G25" s="65"/>
+    </row>
+    <row r="26" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="35"/>
+      <c r="B26" s="28">
         <v>2</v>
       </c>
-      <c r="C26" s="76" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="78"/>
-    </row>
-    <row r="27" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="27">
+      <c r="C26" s="149" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="150"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="151"/>
+      <c r="G26" s="86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="35"/>
+      <c r="B27" s="28">
         <v>3</v>
       </c>
-      <c r="C27" s="76"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="78"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="34"/>
-      <c r="B28" s="29">
+      <c r="C27" s="149"/>
+      <c r="D27" s="150"/>
+      <c r="E27" s="150" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="151"/>
+      <c r="G27" s="86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="36"/>
+      <c r="B28" s="30">
         <v>4</v>
       </c>
-      <c r="C28" s="216"/>
-      <c r="D28" s="217"/>
-      <c r="E28" s="217"/>
-      <c r="F28" s="218"/>
-    </row>
-    <row r="29" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="31">
+      <c r="C28" s="226"/>
+      <c r="D28" s="227"/>
+      <c r="E28" s="227"/>
+      <c r="F28" s="228"/>
+      <c r="G28" s="64"/>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="32">
         <v>2</v>
       </c>
-      <c r="C29" s="141" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="142"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="143"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="36"/>
-      <c r="B30" s="27">
+      <c r="C29" s="189" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="190"/>
+      <c r="E29" s="190"/>
+      <c r="F29" s="191"/>
+      <c r="G29" s="85" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="38"/>
+      <c r="B30" s="28">
         <v>3</v>
       </c>
-      <c r="C30" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="78"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="37"/>
-      <c r="B31" s="29">
+      <c r="C30" s="149" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="150"/>
+      <c r="E30" s="150"/>
+      <c r="F30" s="151"/>
+      <c r="G30" s="86" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="39"/>
+      <c r="B31" s="30">
         <v>3</v>
       </c>
-      <c r="C31" s="215"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75"/>
-    </row>
-    <row r="32" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="57"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="209"/>
-      <c r="D32" s="210"/>
-      <c r="E32" s="210"/>
-      <c r="F32" s="211"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="55"/>
-      <c r="B33" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="212" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="213"/>
-      <c r="E33" s="213"/>
-      <c r="F33" s="214"/>
-    </row>
-    <row r="34" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="65" t="s">
+      <c r="C31" s="225"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="64"/>
+    </row>
+    <row r="32" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="219"/>
+      <c r="D32" s="220"/>
+      <c r="E32" s="220"/>
+      <c r="F32" s="221"/>
+      <c r="G32" s="63"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="59"/>
+      <c r="B33" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="222" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="66"/>
-      <c r="C34" s="205" t="s">
+      <c r="D33" s="223"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="224"/>
+      <c r="G33" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="205"/>
-      <c r="E34" s="205"/>
-      <c r="F34" s="205"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="75"/>
+      <c r="C34" s="215" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="215"/>
+      <c r="E34" s="215"/>
+      <c r="F34" s="215"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>15</v>
       </c>
@@ -3659,6 +4036,22 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C32:F32"/>
@@ -3671,22 +4064,6 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3717,7 +4094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3726,12 +4103,13 @@
     <col min="4" max="4" width="20.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="20.140625" style="2" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="2"/>
-    <col min="10" max="10" width="8.85546875" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="10" width="9.140625" style="2"/>
+    <col min="11" max="11" width="8.85546875" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3739,15 +4117,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3755,39 +4133,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3797,394 +4175,476 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="189" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="189"/>
-      <c r="E8" s="189"/>
-      <c r="F8" s="189"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="235" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="235"/>
+      <c r="E8" s="235"/>
+      <c r="F8" s="235"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="54"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="D9" s="56"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="26">
         <v>2</v>
       </c>
-      <c r="C10" s="222"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="224"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27">
+      <c r="C10" s="259"/>
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="34"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28">
         <v>3</v>
       </c>
-      <c r="C11" s="219" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="220"/>
-      <c r="E11" s="220"/>
-      <c r="F11" s="221"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27">
+      <c r="C11" s="245" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="247"/>
+      <c r="G11" s="89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28">
         <v>4</v>
       </c>
-      <c r="C12" s="219" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="220"/>
-      <c r="E12" s="220"/>
-      <c r="F12" s="221"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27">
+      <c r="C12" s="245" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="246"/>
+      <c r="E12" s="246"/>
+      <c r="F12" s="247"/>
+      <c r="G12" s="89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
         <v>5</v>
       </c>
-      <c r="C13" s="219" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="220"/>
-      <c r="E13" s="220"/>
-      <c r="F13" s="221"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29">
+      <c r="C13" s="245" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <v>7</v>
       </c>
-      <c r="C14" s="76" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="31">
+      <c r="C14" s="149" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="92" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="32">
         <v>2</v>
       </c>
-      <c r="C15" s="141" t="s">
+      <c r="C15" s="189" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="190"/>
+      <c r="E15" s="190"/>
+      <c r="F15" s="191"/>
+      <c r="G15" s="96" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28">
+        <v>3</v>
+      </c>
+      <c r="C16" s="167" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="168"/>
+      <c r="E16" s="168"/>
+      <c r="F16" s="169"/>
+      <c r="G16" s="91" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28">
+        <v>4</v>
+      </c>
+      <c r="C17" s="149" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="150"/>
+      <c r="E17" s="150"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="91" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28">
+        <v>5</v>
+      </c>
+      <c r="C18" s="167" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" s="168"/>
+      <c r="E18" s="168"/>
+      <c r="F18" s="169"/>
+      <c r="G18" s="89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="33"/>
+      <c r="B19" s="30">
+        <v>6</v>
+      </c>
+      <c r="C19" s="98" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="95" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="32">
+        <v>1</v>
+      </c>
+      <c r="C20" s="189" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="190"/>
+      <c r="E20" s="190"/>
+      <c r="F20" s="191"/>
+      <c r="G20" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="143"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27">
+    </row>
+    <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28">
+        <v>2</v>
+      </c>
+      <c r="C21" s="167" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="168"/>
+      <c r="E21" s="168"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28">
         <v>3</v>
       </c>
-      <c r="C16" s="158" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="159"/>
-      <c r="E16" s="159"/>
-      <c r="F16" s="160"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27">
+      <c r="C22" s="149" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="150"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="151"/>
+      <c r="G22" s="89" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28">
         <v>4</v>
       </c>
-      <c r="C17" s="76" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="78"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27">
+      <c r="C23" s="212" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="213"/>
+      <c r="E23" s="213"/>
+      <c r="F23" s="214"/>
+      <c r="G23" s="89" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="33"/>
+      <c r="B24" s="30">
         <v>5</v>
       </c>
-      <c r="C18" s="158" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="159"/>
-      <c r="E18" s="159"/>
-      <c r="F18" s="160"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="32"/>
-      <c r="B19" s="29">
+      <c r="C24" s="252" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="253"/>
+      <c r="E24" s="253"/>
+      <c r="F24" s="254"/>
+      <c r="G24" s="92" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="32">
+        <v>2</v>
+      </c>
+      <c r="C25" s="189" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="190"/>
+      <c r="E25" s="190"/>
+      <c r="F25" s="191"/>
+      <c r="G25" s="90" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="27"/>
+      <c r="B26" s="28">
+        <v>3</v>
+      </c>
+      <c r="C26" s="149" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="150"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="151"/>
+      <c r="G26" s="91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="27"/>
+      <c r="B27" s="28">
+        <v>4</v>
+      </c>
+      <c r="C27" s="245" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="247"/>
+      <c r="G27" s="91" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="76"/>
+      <c r="B28" s="47">
+        <v>5</v>
+      </c>
+      <c r="C28" s="149" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="150"/>
+      <c r="E28" s="150"/>
+      <c r="F28" s="151"/>
+      <c r="G28" s="91" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="32">
+        <v>2</v>
+      </c>
+      <c r="C29" s="258" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="237"/>
+      <c r="E29" s="237"/>
+      <c r="F29" s="238"/>
+      <c r="G29" s="90" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="35"/>
+      <c r="B30" s="26">
+        <v>3</v>
+      </c>
+      <c r="C30" s="245" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="246"/>
+      <c r="E30" s="246"/>
+      <c r="F30" s="247"/>
+      <c r="G30" s="89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="35"/>
+      <c r="B31" s="28">
+        <v>4</v>
+      </c>
+      <c r="C31" s="149" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="150"/>
+      <c r="E31" s="150" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" s="151"/>
+      <c r="G31" s="91" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="36"/>
+      <c r="B32" s="30">
+        <v>5</v>
+      </c>
+      <c r="C32" s="145" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="146"/>
+      <c r="E32" s="146" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="251"/>
+      <c r="G32" s="94" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="32">
+        <v>3</v>
+      </c>
+      <c r="C33" s="255" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="256"/>
+      <c r="E33" s="256"/>
+      <c r="F33" s="257"/>
+      <c r="G33" s="87" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="38"/>
+      <c r="B34" s="28">
+        <v>4</v>
+      </c>
+      <c r="C34" s="167" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="168"/>
+      <c r="E34" s="168"/>
+      <c r="F34" s="169"/>
+      <c r="G34" s="89" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="97"/>
+      <c r="B35" s="47">
+        <v>5</v>
+      </c>
+      <c r="C35" s="167" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" s="168"/>
+      <c r="E35" s="168"/>
+      <c r="F35" s="169"/>
+      <c r="G35" s="95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="39"/>
+      <c r="B36" s="30">
         <v>6</v>
       </c>
-      <c r="C19" s="122" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="124"/>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="31">
-        <v>1</v>
-      </c>
-      <c r="C20" s="141" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="142"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="143"/>
-    </row>
-    <row r="21" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27">
-        <v>2</v>
-      </c>
-      <c r="C21" s="158" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="160"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27">
-        <v>3</v>
-      </c>
-      <c r="C22" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="78"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27">
-        <v>4</v>
-      </c>
-      <c r="C23" s="167" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="168"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="169"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="32"/>
-      <c r="B24" s="29">
-        <v>5</v>
-      </c>
-      <c r="C24" s="229" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="230"/>
-      <c r="E24" s="230"/>
-      <c r="F24" s="231"/>
-    </row>
-    <row r="25" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="31">
-        <v>2</v>
-      </c>
-      <c r="C25" s="141" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="142"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="143"/>
-    </row>
-    <row r="26" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27">
-        <v>3</v>
-      </c>
-      <c r="C26" s="76" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="78"/>
-    </row>
-    <row r="27" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27">
-        <v>4</v>
-      </c>
-      <c r="C27" s="219" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="220"/>
-      <c r="E27" s="220"/>
-      <c r="F27" s="221"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="67"/>
-      <c r="B28" s="44">
-        <v>5</v>
-      </c>
-      <c r="C28" s="76" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="31">
-        <v>2</v>
-      </c>
-      <c r="C29" s="235" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="191"/>
-      <c r="E29" s="191"/>
-      <c r="F29" s="192"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="33"/>
-      <c r="B30" s="25">
-        <v>3</v>
-      </c>
-      <c r="C30" s="219" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="220"/>
-      <c r="E30" s="220"/>
-      <c r="F30" s="221"/>
-    </row>
-    <row r="31" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="33"/>
-      <c r="B31" s="27">
-        <v>4</v>
-      </c>
-      <c r="C31" s="76" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77" t="s">
-        <v>113</v>
-      </c>
-      <c r="F31" s="78"/>
-    </row>
-    <row r="32" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="34"/>
-      <c r="B32" s="29">
-        <v>5</v>
-      </c>
-      <c r="C32" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" s="228"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" s="31">
-        <v>3</v>
-      </c>
-      <c r="C33" s="232" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="234"/>
-    </row>
-    <row r="34" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="36"/>
-      <c r="B34" s="27">
-        <v>4</v>
-      </c>
-      <c r="C34" s="158" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" s="159"/>
-      <c r="E34" s="159"/>
-      <c r="F34" s="160"/>
-    </row>
-    <row r="35" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="71"/>
-      <c r="B35" s="44">
-        <v>5</v>
-      </c>
-      <c r="C35" s="158" t="s">
-        <v>105</v>
-      </c>
-      <c r="D35" s="159"/>
-      <c r="E35" s="159"/>
-      <c r="F35" s="160"/>
-    </row>
-    <row r="36" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="37"/>
-      <c r="B36" s="29">
-        <v>6</v>
-      </c>
-      <c r="C36" s="225" t="s">
-        <v>105</v>
-      </c>
-      <c r="D36" s="226"/>
-      <c r="E36" s="226"/>
-      <c r="F36" s="227"/>
-    </row>
-    <row r="37" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C36" s="248" t="s">
+        <v>135</v>
+      </c>
+      <c r="D36" s="249"/>
+      <c r="E36" s="249"/>
+      <c r="F36" s="250"/>
+      <c r="G36" s="92" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>15</v>
       </c>
@@ -4194,14 +4654,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
@@ -4218,12 +4676,14 @@
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:F18"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
